--- a/artfynd/A 30014-2023 artfynd.xlsx
+++ b/artfynd/A 30014-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121149383</v>
       </c>
       <c r="B2" t="n">
-        <v>97031</v>
+        <v>97041</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 30014-2023 artfynd.xlsx
+++ b/artfynd/A 30014-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121149383</v>
       </c>
       <c r="B2" t="n">
-        <v>97041</v>
+        <v>97054</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 30014-2023 artfynd.xlsx
+++ b/artfynd/A 30014-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121149383</v>
       </c>
       <c r="B2" t="n">
-        <v>97054</v>
+        <v>97055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 30014-2023 artfynd.xlsx
+++ b/artfynd/A 30014-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121149383</v>
       </c>
       <c r="B2" t="n">
-        <v>97055</v>
+        <v>97058</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
